--- a/Dday 검증용 엑셀_수동.xlsx
+++ b/Dday 검증용 엑셀_수동.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2. Git\AndroidApp_Dday\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE88A4FA-42B8-4357-992C-C0F2D6248410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F6DE7E-8513-4830-9250-A06222E79206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="5025" windowWidth="15720" windowHeight="11970" xr2:uid="{ADE3DAAE-220F-4E59-ADED-BE4346C5618B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{ADE3DAAE-220F-4E59-ADED-BE4346C5618B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1월 8일" sheetId="2" r:id="rId1"/>
+    <sheet name="1월 6일" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1월 6일'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1월 8일'!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="9">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,7 +86,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,8 +102,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,6 +124,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -124,12 +139,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -142,11 +160,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -483,6 +515,1028 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED54B186-DAB1-49A7-A250-848FFBD4C52E}">
+  <dimension ref="A1:F55"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="21.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3">
+        <v>36</v>
+      </c>
+      <c r="E2" s="3">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>52</v>
+      </c>
+      <c r="D3">
+        <v>35</v>
+      </c>
+      <c r="E3">
+        <v>49</v>
+      </c>
+      <c r="F3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>46030</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>51</v>
+      </c>
+      <c r="D4" s="5">
+        <v>34</v>
+      </c>
+      <c r="E4" s="5">
+        <v>48</v>
+      </c>
+      <c r="F4" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>33</v>
+      </c>
+      <c r="E5">
+        <v>47</v>
+      </c>
+      <c r="F5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>48</v>
+      </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>47</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>43</v>
+      </c>
+      <c r="F9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>45</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>42</v>
+      </c>
+      <c r="F10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>44</v>
+      </c>
+      <c r="D11">
+        <v>29</v>
+      </c>
+      <c r="E11">
+        <v>41</v>
+      </c>
+      <c r="F11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>43</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>41</v>
+      </c>
+      <c r="E14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <v>27</v>
+      </c>
+      <c r="E15">
+        <v>37</v>
+      </c>
+      <c r="F15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>39</v>
+      </c>
+      <c r="D16">
+        <v>26</v>
+      </c>
+      <c r="E16">
+        <v>36</v>
+      </c>
+      <c r="F16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>38</v>
+      </c>
+      <c r="D17">
+        <v>25</v>
+      </c>
+      <c r="E17">
+        <v>35</v>
+      </c>
+      <c r="F17">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>37</v>
+      </c>
+      <c r="D18">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>34</v>
+      </c>
+      <c r="F18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>36</v>
+      </c>
+      <c r="D19">
+        <v>23</v>
+      </c>
+      <c r="E19">
+        <v>33</v>
+      </c>
+      <c r="F19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46046</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3">
+        <v>35</v>
+      </c>
+      <c r="E20" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>34</v>
+      </c>
+      <c r="E21">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>33</v>
+      </c>
+      <c r="D22">
+        <v>22</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>32</v>
+      </c>
+      <c r="D23">
+        <v>21</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+      <c r="F23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>31</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
+        <v>28</v>
+      </c>
+      <c r="F24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>19</v>
+      </c>
+      <c r="E25">
+        <v>27</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>18</v>
+      </c>
+      <c r="E26">
+        <v>26</v>
+      </c>
+      <c r="F26">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46053</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>28</v>
+      </c>
+      <c r="E27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>17</v>
+      </c>
+      <c r="E29">
+        <v>23</v>
+      </c>
+      <c r="F29">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>25</v>
+      </c>
+      <c r="D30">
+        <v>16</v>
+      </c>
+      <c r="E30">
+        <v>22</v>
+      </c>
+      <c r="F30">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>24</v>
+      </c>
+      <c r="D31">
+        <v>15</v>
+      </c>
+      <c r="E31">
+        <v>21</v>
+      </c>
+      <c r="F31">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>14</v>
+      </c>
+      <c r="E32">
+        <v>20</v>
+      </c>
+      <c r="F32">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>22</v>
+      </c>
+      <c r="D33">
+        <v>13</v>
+      </c>
+      <c r="E33">
+        <v>19</v>
+      </c>
+      <c r="F33">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46060</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>21</v>
+      </c>
+      <c r="E34">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>46061</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>20</v>
+      </c>
+      <c r="E35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>19</v>
+      </c>
+      <c r="D36">
+        <v>12</v>
+      </c>
+      <c r="E36">
+        <v>16</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37">
+        <v>18</v>
+      </c>
+      <c r="D37">
+        <v>11</v>
+      </c>
+      <c r="E37">
+        <v>15</v>
+      </c>
+      <c r="F37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>17</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38">
+        <v>14</v>
+      </c>
+      <c r="F38">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>16</v>
+      </c>
+      <c r="D39">
+        <v>9</v>
+      </c>
+      <c r="E39">
+        <v>13</v>
+      </c>
+      <c r="F39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40">
+        <v>15</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <v>12</v>
+      </c>
+      <c r="F40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41">
+        <v>14</v>
+      </c>
+      <c r="E41">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>46068</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>13</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>11</v>
+      </c>
+      <c r="F44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>46071</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="3">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <v>9</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>8</v>
+      </c>
+      <c r="F47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46074</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48">
+        <v>7</v>
+      </c>
+      <c r="E48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F55" xr:uid="{69411451-1C9B-4835-B3AD-7035983D6237}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F55">
+      <sortCondition ref="A1:A55"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69411451-1C9B-4835-B3AD-7035983D6237}">
   <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1498,7 +2552,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
